--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41217-2026 artfynd.xlsx
+++ b/artfynd/A 41217-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105913</v>
       </c>
       <c r="B2" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
